--- a/data/SHE.xlsx
+++ b/data/SHE.xlsx
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>W L A M SIRIWARDANA</t>
+          <t>W L A M SIRIWARDANE</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -1652,21 +1652,62 @@
       <c r="Z11" s="31" t="n"/>
       <c r="AA11" s="32" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>920272363V</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dependant</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="C1:C2"/>
+    <mergeCell ref="U1:Y1"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="U1:Y1"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="AA1:AA2"/>
     <mergeCell ref="O1:O2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
